--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260707.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260707.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>34,299</t>
+          <t>34,140</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.52%</t>
+          <t>11.03%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>82,908</t>
+          <t>82,522</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>9.80%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>95,633</t>
+          <t>95,188</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.88%</t>
+          <t>8.73%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>37,644</t>
+          <t>37,469</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.40%</t>
+          <t>7.38%</t>
         </is>
       </c>
     </row>
@@ -699,56 +699,56 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>206,623</t>
+          <t>205,662</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.27%</t>
+          <t>5.46%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>BE UN</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Bloom Energy Corp</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>51,874</t>
+          <t>109,379</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.46%</t>
+          <t>4.21%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>BE UN</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>Bloom Energy Corp</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>109,890</t>
+          <t>51,633</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>4.18%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>119,180</t>
+          <t>118,626</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>3.46%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>20,518</t>
+          <t>20,423</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.93%</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>62,423</t>
+          <t>62,133</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>123,963</t>
+          <t>123,386</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>57,413</t>
+          <t>57,147</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>144,309</t>
+          <t>143,639</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>25,732</t>
+          <t>25,612</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>23,855</t>
+          <t>23,744</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -941,78 +941,78 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>65,964</t>
+          <t>65,657</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>12,003</t>
+          <t>38,760</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>PEG US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>大眾服務企業集團公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>38,941</t>
+          <t>52,414</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>PEG US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>大眾服務企業集團公司</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>52,659</t>
+          <t>11,947</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>54,219</t>
+          <t>53,967</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>34,421</t>
+          <t>34,261</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>81,526</t>
+          <t>81,147</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1095,34 +1095,34 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>53,001</t>
+          <t>52,755</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>5,210</t>
+          <t>32,084</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1139,34 +1139,34 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>23,566</t>
+          <t>23,457</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>32,234</t>
+          <t>5,186</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>49,791</t>
+          <t>49,559</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>21,926</t>
+          <t>21,824</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>29,189</t>
+          <t>29,053</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1249,122 +1249,122 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>100,649</t>
+          <t>100,181</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>14,031</t>
+          <t>79,116</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>9,533</t>
+          <t>31,946</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>11,272</t>
+          <t>13,966</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>79,486</t>
+          <t>9,489</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>32,095</t>
+          <t>11,219</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>154,520</t>
+          <t>153,802</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>32,494</t>
+          <t>32,343</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>27,296</t>
+          <t>27,169</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>46,038</t>
+          <t>45,824</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>14,212</t>
+          <t>14,146</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>17,075</t>
+          <t>16,995</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>7,228</t>
+          <t>7,195</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>6,223</t>
+          <t>6,194</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>3,866</t>
+          <t>3,848</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>100,055</t>
+          <t>99,589</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>24,901</t>
+          <t>24,785</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>3,006</t>
+          <t>2,992</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>8,492</t>
+          <t>8,453</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>19,537</t>
+          <t>19,446</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>40,509</t>
+          <t>40,321</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>131,169,356</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
